--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_5_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_5_IN_Piura.xlsx
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>25.31</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C13" s="31">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>63.22</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>11.32</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>295.7261</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>0.4454</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1965,11 +1965,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>295.2807</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>99.85</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>295.8609</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2286,6 +2286,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2610,6 +2611,7 @@
       <c r="F19" s="17" t="inlineStr"/>
       <c r="G19" s="17" t="inlineStr"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -2658,6 +2660,7 @@
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24" ht="120" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -2976,11 +2979,11 @@
       </c>
       <c r="B15" s="33">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>1553.97</v>
       </c>
       <c r="C15" s="23">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -2990,19 +2993,19 @@
       <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17">
         <f>ROUND(AVERAGE(F10:F14),2)</f>
-        <v/>
+        <v>18.02</v>
       </c>
       <c r="G15" s="22">
         <f>ROUND(AVERAGE(G10:G14),4)</f>
-        <v/>
+        <v>0.3393</v>
       </c>
       <c r="H15" s="23">
         <f>ROUND(AVERAGE(H10:H14),2)</f>
-        <v/>
+        <v>2.45</v>
       </c>
       <c r="I15" s="23">
         <f>ROUND(AVERAGE(I10:I14),2)</f>
-        <v/>
+        <v>97.63</v>
       </c>
     </row>
     <row r="16"/>
